--- a/doscs/tabeldatappl.xlsx
+++ b/doscs/tabeldatappl.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMESTER 2\TUGAS\PL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMESTER 2\isp-management\doscs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECACA458-22E1-4E48-9FBB-FE349A6BAACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{438B3D15-8EF6-494B-8CEF-3F5937F00E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="504" windowWidth="23256" windowHeight="14004" xr2:uid="{1A2704CE-872D-44EB-9171-EA87FD1697CC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>pelanggan</t>
   </si>
@@ -133,6 +133,21 @@
   </si>
   <si>
     <t>detail_kendala_sigkat</t>
+  </si>
+  <si>
+    <t>id_queue</t>
+  </si>
+  <si>
+    <t>id_mt</t>
+  </si>
+  <si>
+    <t>detail_alat_mt</t>
+  </si>
+  <si>
+    <t>id_detai</t>
+  </si>
+  <si>
+    <t>jumlah</t>
   </si>
 </sst>
 </file>
@@ -148,7 +163,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,6 +185,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -228,17 +249,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF00FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -547,40 +573,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025CED8D-1138-4CE9-ADC2-DA119C52CA5A}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" customWidth="1"/>
     <col min="8" max="8" width="15.21875" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="18.77734375" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="20.5546875" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" customWidth="1"/>
     <col min="15" max="15" width="14.109375" customWidth="1"/>
     <col min="16" max="16" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -598,6 +625,9 @@
       </c>
       <c r="E2" s="5" t="s">
         <v>21</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>8</v>
@@ -619,6 +649,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -631,6 +662,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -638,17 +670,17 @@
       <c r="L4" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="H7" s="6" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="H7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -683,10 +715,10 @@
       <c r="K9" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="7"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -695,19 +727,19 @@
       <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="7"/>
-      <c r="H13" s="8" t="s">
+      <c r="C13" s="6"/>
+      <c r="H13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H14" s="1" t="s">
@@ -734,13 +766,13 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -749,19 +781,19 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -777,29 +809,29 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -810,11 +842,11 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -826,14 +858,39 @@
       <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="H23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
+      <c r="H24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="H23:K23"/>
     <mergeCell ref="H13:L13"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="A11:B11"/>
@@ -841,7 +898,8 @@
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="H7:K7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
